--- a/Cash Flow 12 Month.xlsx
+++ b/Cash Flow 12 Month.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37EF3C2-BC18-4259-8E74-754A09432400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1299605-D5C7-4DF8-8934-5C058B721247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB791584-A06D-4D2A-A996-547D16A53797}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>بنك الراجحي</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Cash beginnin</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -755,7 +758,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
+      <c r="A1" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="B1" s="18">
         <v>46265</v>
       </c>

--- a/Cash Flow 12 Month.xlsx
+++ b/Cash Flow 12 Month.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1299605-D5C7-4DF8-8934-5C058B721247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43D42F8-4FC3-40ED-BE66-17204962553D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB791584-A06D-4D2A-A996-547D16A53797}"/>
   </bookViews>
@@ -751,10 +751,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -814,43 +814,43 @@
       </c>
       <c r="C2" s="2">
         <f>B46</f>
-        <v>525707</v>
+        <v>-3415838</v>
       </c>
       <c r="D2" s="2">
         <f t="shared" ref="D2:L2" si="1">C46</f>
-        <v>191123</v>
+        <v>2066912</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" si="1"/>
-        <v>5073821</v>
+        <v>6934610</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" si="1"/>
-        <v>7180571</v>
+        <v>9026360</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" si="1"/>
-        <v>11360571</v>
+        <v>13191360</v>
       </c>
       <c r="H2" s="2">
         <f t="shared" si="1"/>
-        <v>11918571</v>
+        <v>15234360</v>
       </c>
       <c r="I2" s="2">
         <f t="shared" si="1"/>
-        <v>9232371</v>
+        <v>14169360</v>
       </c>
       <c r="J2" s="2">
         <f t="shared" si="1"/>
-        <v>7391271</v>
+        <v>13654360</v>
       </c>
       <c r="K2" s="2">
         <f t="shared" si="1"/>
-        <v>8766284</v>
+        <v>12608173</v>
       </c>
       <c r="L2" s="2">
         <f t="shared" si="1"/>
-        <v>9946284</v>
+        <v>12577573</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4">
-        <v>55000</v>
+        <v>19000</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -875,7 +875,9 @@
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="5">
+        <v>200000</v>
+      </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -891,7 +893,9 @@
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="5">
+        <v>-400000</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -907,7 +911,9 @@
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="5">
+        <v>56864</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -924,10 +930,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4">
-        <v>125117</v>
+        <v>172000</v>
       </c>
       <c r="C7" s="4">
-        <v>268058</v>
+        <v>300000</v>
       </c>
       <c r="D7" s="4">
         <v>294948</v>
@@ -970,7 +976,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>3520000</v>
+        <v>1700000</v>
       </c>
       <c r="C9" s="4">
         <v>3160000</v>
@@ -1105,10 +1111,10 @@
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4">
         <v>500000</v>
       </c>
-      <c r="C15" s="5"/>
       <c r="D15" s="4">
         <v>500000</v>
       </c>
@@ -1179,47 +1185,47 @@
       </c>
       <c r="B19" s="7">
         <f t="shared" ref="B19:L19" si="2">SUM(B2:B18)</f>
-        <v>4200117</v>
+        <v>1747864</v>
       </c>
       <c r="C19" s="7">
         <f t="shared" si="2"/>
-        <v>5793765</v>
+        <v>2384162</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="2"/>
-        <v>5356071</v>
+        <v>7231860</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="2"/>
-        <v>9133821</v>
+        <v>10994610</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="2"/>
-        <v>12910571</v>
+        <v>14756360</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="2"/>
-        <v>14280571</v>
+        <v>16111360</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="2"/>
-        <v>14658571</v>
+        <v>17974360</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="2"/>
-        <v>10822371</v>
+        <v>15759360</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="2"/>
-        <v>8871284</v>
+        <v>15134373</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="2"/>
-        <v>10046284</v>
+        <v>13888173</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="2"/>
-        <v>10076284</v>
+        <v>12707573</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1250,7 +1256,9 @@
       <c r="A21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="9"/>
+      <c r="B21" s="9">
+        <v>30000</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -1266,7 +1274,9 @@
       <c r="A22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="9"/>
+      <c r="B22" s="9">
+        <v>30000</v>
+      </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -1283,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="11">
-        <v>313850</v>
+        <v>132250</v>
       </c>
       <c r="C23" s="11">
         <v>132250</v>
@@ -1308,12 +1318,8 @@
       <c r="A24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="11">
-        <v>2978560</v>
-      </c>
-      <c r="C24" s="11">
-        <v>5204892</v>
-      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -1328,8 +1334,10 @@
       <c r="A25" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="11">
+        <v>4464452</v>
+      </c>
+      <c r="C25" s="11"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -1350,39 +1358,38 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="11">
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11">
+        <f>1210600+1210600</f>
         <v>2421200</v>
       </c>
-      <c r="I26" s="11">
+      <c r="K26" s="11">
         <v>1210600</v>
       </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
+      <c r="L26" s="9">
+        <v>605300</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="9"/>
-      <c r="C27" s="11">
-        <v>115500</v>
-      </c>
+      <c r="C27" s="11"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="11">
+      <c r="G27" s="11"/>
+      <c r="H27" s="11">
         <v>1500000</v>
       </c>
-      <c r="H27" s="11">
-        <v>700000</v>
-      </c>
-      <c r="I27" s="12">
-        <v>115500</v>
-      </c>
+      <c r="I27" s="12"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
+      <c r="L27" s="12">
+        <v>115500</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
@@ -1426,7 +1433,9 @@
       <c r="A29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="9"/>
+      <c r="B29" s="9">
+        <v>100000</v>
+      </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -1471,22 +1480,22 @@
         <v>25</v>
       </c>
       <c r="B31" s="11">
-        <v>35000</v>
+        <v>92000</v>
       </c>
       <c r="C31" s="11">
-        <v>35000</v>
+        <v>70000</v>
       </c>
       <c r="D31" s="11">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="E31" s="11">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="F31" s="11">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="G31" s="11">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -1498,9 +1507,7 @@
       <c r="A32" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="11">
-        <v>32000</v>
-      </c>
+      <c r="B32" s="11"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -1734,47 +1741,47 @@
       </c>
       <c r="B44" s="14">
         <f>SUM(B20:B43)</f>
-        <v>3674410</v>
+        <v>5163702</v>
       </c>
       <c r="C44" s="14">
         <f t="shared" ref="C44:L44" si="3">SUM(C20:C43)</f>
-        <v>5602642</v>
+        <v>317250</v>
       </c>
       <c r="D44" s="14">
         <f t="shared" si="3"/>
-        <v>282250</v>
+        <v>297250</v>
       </c>
       <c r="E44" s="14">
         <f t="shared" si="3"/>
-        <v>1953250</v>
+        <v>1968250</v>
       </c>
       <c r="F44" s="14">
         <f t="shared" si="3"/>
-        <v>1550000</v>
+        <v>1565000</v>
       </c>
       <c r="G44" s="14">
         <f t="shared" si="3"/>
-        <v>2362000</v>
+        <v>877000</v>
       </c>
       <c r="H44" s="14">
         <f t="shared" si="3"/>
-        <v>5426200</v>
+        <v>3805000</v>
       </c>
       <c r="I44" s="14">
         <f t="shared" si="3"/>
-        <v>3431100</v>
+        <v>2105000</v>
       </c>
       <c r="J44" s="14">
         <f t="shared" si="3"/>
-        <v>105000</v>
+        <v>2526200</v>
       </c>
       <c r="K44" s="14">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>1310600</v>
       </c>
       <c r="L44" s="14">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>1220800</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -1783,47 +1790,47 @@
       </c>
       <c r="B46" s="16">
         <f>B19-B44</f>
-        <v>525707</v>
+        <v>-3415838</v>
       </c>
       <c r="C46" s="16">
         <f t="shared" ref="C46:L46" si="4">C19-C44</f>
-        <v>191123</v>
+        <v>2066912</v>
       </c>
       <c r="D46" s="16">
         <f t="shared" si="4"/>
-        <v>5073821</v>
+        <v>6934610</v>
       </c>
       <c r="E46" s="16">
         <f t="shared" si="4"/>
-        <v>7180571</v>
+        <v>9026360</v>
       </c>
       <c r="F46" s="16">
         <f t="shared" si="4"/>
-        <v>11360571</v>
+        <v>13191360</v>
       </c>
       <c r="G46" s="16">
         <f t="shared" si="4"/>
-        <v>11918571</v>
+        <v>15234360</v>
       </c>
       <c r="H46" s="16">
         <f t="shared" si="4"/>
-        <v>9232371</v>
+        <v>14169360</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="4"/>
-        <v>7391271</v>
+        <v>13654360</v>
       </c>
       <c r="J46" s="16">
         <f t="shared" si="4"/>
-        <v>8766284</v>
+        <v>12608173</v>
       </c>
       <c r="K46" s="16">
         <f t="shared" si="4"/>
-        <v>9946284</v>
+        <v>12577573</v>
       </c>
       <c r="L46" s="16">
         <f t="shared" si="4"/>
-        <v>9576284</v>
+        <v>11486773</v>
       </c>
     </row>
   </sheetData>

--- a/Cash Flow 12 Month.xlsx
+++ b/Cash Flow 12 Month.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43D42F8-4FC3-40ED-BE66-17204962553D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF11397-94D6-4277-B50C-F1EFCF61E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB791584-A06D-4D2A-A996-547D16A53797}"/>
   </bookViews>
@@ -814,43 +814,43 @@
       </c>
       <c r="C2" s="2">
         <f>B46</f>
-        <v>-3415838</v>
+        <v>-3402338</v>
       </c>
       <c r="D2" s="2">
         <f t="shared" ref="D2:L2" si="1">C46</f>
-        <v>2066912</v>
+        <v>2080412</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" si="1"/>
-        <v>6934610</v>
+        <v>6948110</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" si="1"/>
-        <v>9026360</v>
+        <v>9039860</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" si="1"/>
-        <v>13191360</v>
+        <v>13204860</v>
       </c>
       <c r="H2" s="2">
         <f t="shared" si="1"/>
-        <v>15234360</v>
+        <v>15247860</v>
       </c>
       <c r="I2" s="2">
         <f t="shared" si="1"/>
-        <v>14169360</v>
+        <v>14182860</v>
       </c>
       <c r="J2" s="2">
         <f t="shared" si="1"/>
-        <v>13654360</v>
+        <v>13667860</v>
       </c>
       <c r="K2" s="2">
         <f t="shared" si="1"/>
-        <v>12608173</v>
+        <v>12621660</v>
       </c>
       <c r="L2" s="2">
         <f t="shared" si="1"/>
-        <v>12577573</v>
+        <v>12591060</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>200000</v>
+        <v>130000</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -912,7 +912,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>56864</v>
+        <v>156864</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -965,9 +965,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="4">
-        <v>13</v>
-      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
@@ -1185,47 +1183,47 @@
       </c>
       <c r="B19" s="7">
         <f t="shared" ref="B19:L19" si="2">SUM(B2:B18)</f>
-        <v>1747864</v>
+        <v>1761364</v>
       </c>
       <c r="C19" s="7">
         <f t="shared" si="2"/>
-        <v>2384162</v>
+        <v>2397662</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="2"/>
-        <v>7231860</v>
+        <v>7245360</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="2"/>
-        <v>10994610</v>
+        <v>11008110</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="2"/>
-        <v>14756360</v>
+        <v>14769860</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="2"/>
-        <v>16111360</v>
+        <v>16124860</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="2"/>
-        <v>17974360</v>
+        <v>17987860</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="2"/>
-        <v>15759360</v>
+        <v>15772860</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="2"/>
-        <v>15134373</v>
+        <v>15147860</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="2"/>
-        <v>13888173</v>
+        <v>13901660</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="2"/>
-        <v>12707573</v>
+        <v>12721060</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1790,47 +1788,47 @@
       </c>
       <c r="B46" s="16">
         <f>B19-B44</f>
-        <v>-3415838</v>
+        <v>-3402338</v>
       </c>
       <c r="C46" s="16">
         <f t="shared" ref="C46:L46" si="4">C19-C44</f>
-        <v>2066912</v>
+        <v>2080412</v>
       </c>
       <c r="D46" s="16">
         <f t="shared" si="4"/>
-        <v>6934610</v>
+        <v>6948110</v>
       </c>
       <c r="E46" s="16">
         <f t="shared" si="4"/>
-        <v>9026360</v>
+        <v>9039860</v>
       </c>
       <c r="F46" s="16">
         <f t="shared" si="4"/>
-        <v>13191360</v>
+        <v>13204860</v>
       </c>
       <c r="G46" s="16">
         <f t="shared" si="4"/>
-        <v>15234360</v>
+        <v>15247860</v>
       </c>
       <c r="H46" s="16">
         <f t="shared" si="4"/>
-        <v>14169360</v>
+        <v>14182860</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="4"/>
-        <v>13654360</v>
+        <v>13667860</v>
       </c>
       <c r="J46" s="16">
         <f t="shared" si="4"/>
-        <v>12608173</v>
+        <v>12621660</v>
       </c>
       <c r="K46" s="16">
         <f t="shared" si="4"/>
-        <v>12577573</v>
+        <v>12591060</v>
       </c>
       <c r="L46" s="16">
         <f t="shared" si="4"/>
-        <v>11486773</v>
+        <v>11500260</v>
       </c>
     </row>
   </sheetData>
